--- a/resultados/altonia/erros_varredura.xlsx
+++ b/resultados/altonia/erros_varredura.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F55"/>
+  <dimension ref="A1:F98"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -456,23 +456,23 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;idStatusLegislacao=1</t>
+          <t>https://altonia.pr.gov.br/cdn-cgi/l/email-protection</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D2" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E2" t="n">
         <v>2</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:18</t>
+          <t>2026-07-29 10:47:09</t>
         </is>
       </c>
     </row>
@@ -484,23 +484,23 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;ano=2021</t>
+          <t>https://www.altonia.pr.gov.br/pagina/_.html</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D3" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E3" t="n">
         <v>2</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:23</t>
+          <t>2026-07-29 10:50:24</t>
         </is>
       </c>
     </row>
@@ -512,23 +512,23 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;ano=2022</t>
+          <t>https://www.altonia.pr.gov.br/noticiasView/16028_.html</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D4" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E4" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:27</t>
+          <t>2026-07-29 10:55:40</t>
         </is>
       </c>
     </row>
@@ -540,23 +540,23 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=604</t>
+          <t>https://www.altonia.pr.gov.br/noticiasView/15987_.html</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D5" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E5" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:33</t>
+          <t>2026-07-29 10:55:45</t>
         </is>
       </c>
     </row>
@@ -568,23 +568,23 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=606</t>
+          <t>https://www.altonia.pr.gov.br/noticiasView/14829_.html</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D6" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E6" t="n">
-        <v>2</v>
+        <v>3</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:37</t>
+          <t>2026-07-29 10:58:23</t>
         </is>
       </c>
     </row>
@@ -596,23 +596,23 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=605</t>
+          <t>https://altonia.pr.gov.br/concursosView/?id=6&amp;fbclid=IwAR20nVDvHUoz44R-jyL3SKB-FAGs285hz2ijxmSz8gl30m0HPHulDCH_W8k</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D7" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E7" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:41</t>
+          <t>2026-07-29 11:32:33</t>
         </is>
       </c>
     </row>
@@ -624,23 +624,23 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=600</t>
+          <t>https://altonia.pr.gov.br/pagina/_.html</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D8" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E8" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:46</t>
+          <t>2026-07-29 11:50:02</t>
         </is>
       </c>
     </row>
@@ -652,23 +652,23 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=594</t>
+          <t>https://altonia.pr.gov.br/noticiasView/16028_.html</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D9" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E9" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:50</t>
+          <t>2026-07-29 11:52:36</t>
         </is>
       </c>
     </row>
@@ -680,23 +680,23 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=592</t>
+          <t>https://altonia.pr.gov.br/noticiasView/15987_.html</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D10" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E10" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>2026-07-29 10:45:54</t>
+          <t>2026-07-29 11:52:38</t>
         </is>
       </c>
     </row>
@@ -708,23 +708,23 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=576</t>
+          <t>https://altonia.pr.gov.br/noticiasView/14829_.html</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D11" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E11" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:00</t>
+          <t>2026-07-29 11:53:55</t>
         </is>
       </c>
     </row>
@@ -736,23 +736,23 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=577</t>
+          <t>https://www.altonia.pr.gov.br/concursos-publicos/</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D12" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E12" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:04</t>
+          <t>2026-07-29 12:08:52</t>
         </is>
       </c>
     </row>
@@ -764,23 +764,23 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=575</t>
+          <t>http://www.altonia.pr.gov.br/concursos-publicos/</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D13" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E13" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:07</t>
+          <t>2026-07-29 12:09:48</t>
         </is>
       </c>
     </row>
@@ -792,23 +792,23 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=579</t>
+          <t>http://www.altonia.pr.gov.br/audiencias-publicas-relatorios/</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D14" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E14" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:13</t>
+          <t>2026-07-29 12:09:48</t>
         </is>
       </c>
     </row>
@@ -820,23 +820,23 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=564</t>
+          <t>http://www.altonia.pr.gov.br/pme-plano-municipal-de-educacao/plano_municipal-educacao/</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D15" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E15" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:17</t>
+          <t>2026-07-29 12:09:51</t>
         </is>
       </c>
     </row>
@@ -848,23 +848,23 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=568</t>
+          <t>http://www.altonia.pr.gov.br/prefeitura-e-sebrae-promovem-capacitacao-sobre-a-redesim/redesim/</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D16" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E16" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:21</t>
+          <t>2026-07-29 12:09:52</t>
         </is>
       </c>
     </row>
@@ -876,23 +876,23 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=552</t>
+          <t>http://www.altonia.pr.gov.br/prefeitura-e-sebrae-promovem-capacitacao-sobre-a-redesim/redesim-1/</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D17" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E17" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:26</t>
+          <t>2026-07-29 12:09:53</t>
         </is>
       </c>
     </row>
@@ -904,23 +904,23 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=551</t>
+          <t>http://www.altonia.pr.gov.br/prefeitura-e-sebrae-promovem-capacitacao-sobre-a-redesim/redesim-2/</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D18" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E18" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:30</t>
+          <t>2026-07-29 12:09:54</t>
         </is>
       </c>
     </row>
@@ -932,23 +932,23 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=554</t>
+          <t>http://www.altonia.pr.gov.br/prefeitura-e-sebrae-promovem-capacitacao-sobre-a-redesim/redesim-3/</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D19" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E19" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:34</t>
+          <t>2026-07-29 12:09:55</t>
         </is>
       </c>
     </row>
@@ -960,23 +960,23 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=535</t>
+          <t>http://www.altonia.pr.gov.br/prefeitura-e-sebrae-promovem-capacitacao-sobre-a-redesim/redesim-4/</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D20" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E20" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:40</t>
+          <t>2026-07-29 12:09:56</t>
         </is>
       </c>
     </row>
@@ -988,23 +988,23 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=530</t>
+          <t>http://www.altonia.pr.gov.br/prefeitura-e-sebrae-promovem-capacitacao-sobre-a-redesim/redesim-5/</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D21" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E21" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:44</t>
+          <t>2026-07-29 12:09:57</t>
         </is>
       </c>
     </row>
@@ -1016,23 +1016,23 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=532</t>
+          <t>http://www.altonia.pr.gov.br/em-altonia-pr-a-mobilizacao-pela-educacao-e-continua/mobilizacao-1/</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D22" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E22" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:48</t>
+          <t>2026-07-29 12:09:58</t>
         </is>
       </c>
     </row>
@@ -1044,23 +1044,23 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;pag=3</t>
+          <t>http://www.altonia.pr.gov.br/em-altonia-pr-a-mobilizacao-pela-educacao-e-continua/mobilizacao-2/</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D23" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E23" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:54</t>
+          <t>2026-07-29 12:09:59</t>
         </is>
       </c>
     </row>
@@ -1072,23 +1072,23 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;pag=4</t>
+          <t>http://www.altonia.pr.gov.br/em-altonia-pr-a-mobilizacao-pela-educacao-e-continua/mobilizacao-3/</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D24" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E24" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F24" t="inlineStr">
         <is>
-          <t>2026-07-29 10:46:58</t>
+          <t>2026-07-29 12:09:59</t>
         </is>
       </c>
     </row>
@@ -1100,23 +1100,23 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;pag=5</t>
+          <t>http://www.altonia.pr.gov.br/em-altonia-pr-a-mobilizacao-pela-educacao-e-continua/mobilizacao-4/</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D25" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E25" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:02</t>
+          <t>2026-07-29 12:10:00</t>
         </is>
       </c>
     </row>
@@ -1128,7 +1128,7 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/cdn-cgi/l/email-protection</t>
+          <t>http://www.altonia.pr.gov.br/em-altonia-pr-a-mobilizacao-pela-educacao-e-continua/mobilizacao-5/</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
@@ -1140,11 +1140,11 @@
         <v>404</v>
       </c>
       <c r="E26" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:09</t>
+          <t>2026-07-29 12:10:01</t>
         </is>
       </c>
     </row>
@@ -1156,23 +1156,23 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;idStatusLegislacao=1</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-controlar-meu-dinheiro-3/oficina-sei-controlar-meu-dinheiro3/</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D27" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E27" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:09</t>
+          <t>2026-07-29 12:10:02</t>
         </is>
       </c>
     </row>
@@ -1184,23 +1184,23 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;ano=2021</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-controlar-meu-dinheiro-3/oficina-sei-controlar-meu-dinheiro2/</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D28" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E28" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:13</t>
+          <t>2026-07-29 12:10:03</t>
         </is>
       </c>
     </row>
@@ -1212,23 +1212,23 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;ano=2022</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-controlar-meu-dinheiro-3/oficina-sei-controlar-meu-dinheiro1/</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D29" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E29" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:17</t>
+          <t>2026-07-29 12:10:04</t>
         </is>
       </c>
     </row>
@@ -1240,23 +1240,23 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=595</t>
+          <t>http://www.altonia.pr.gov.br/seminario-de-credito/seminario-de-credito-2/</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D30" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E30" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:23</t>
+          <t>2026-07-29 12:10:05</t>
         </is>
       </c>
     </row>
@@ -1268,23 +1268,23 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=598</t>
+          <t>http://www.altonia.pr.gov.br/seminario-de-credito/seminario-de-credito-1/</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D31" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E31" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:27</t>
+          <t>2026-07-29 12:10:06</t>
         </is>
       </c>
     </row>
@@ -1296,23 +1296,23 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=597</t>
+          <t>http://www.altonia.pr.gov.br/2a-audiencia-publica-2015/audiencia-publica-2015/</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D32" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E32" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F32" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:31</t>
+          <t>2026-07-29 12:10:07</t>
         </is>
       </c>
     </row>
@@ -1324,23 +1324,23 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=586</t>
+          <t>http://www.altonia.pr.gov.br/4a-caminhada-na-natureza/arte-folder-caminhada-da-natureza-1/</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D33" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E33" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F33" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:37</t>
+          <t>2026-07-29 12:10:08</t>
         </is>
       </c>
     </row>
@@ -1352,23 +1352,23 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=585</t>
+          <t>http://www.altonia.pr.gov.br/final-do-campeonato-municipal-genival-soares-de-oliveira-de-futsal/genival-soares-de-oliveira-1/</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D34" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E34" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F34" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:40</t>
+          <t>2026-07-29 12:10:09</t>
         </is>
       </c>
     </row>
@@ -1380,23 +1380,23 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=584</t>
+          <t>http://www.altonia.pr.gov.br/futsal-feminino-campeao/futsal-feminino-campeao-1/</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D35" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E35" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F35" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:44</t>
+          <t>2026-07-29 12:10:16</t>
         </is>
       </c>
     </row>
@@ -1408,23 +1408,23 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=572</t>
+          <t>http://www.altonia.pr.gov.br/futsal-feminino-campeao/futsal-feminino-campeao-2/</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D36" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F36" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:51</t>
+          <t>2026-07-29 12:10:17</t>
         </is>
       </c>
     </row>
@@ -1436,23 +1436,23 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=563</t>
+          <t>http://www.altonia.pr.gov.br/futsal-feminino-campeao/futsal-feminino-campeao-3/</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D37" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E37" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F37" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:55</t>
+          <t>2026-07-29 12:10:18</t>
         </is>
       </c>
     </row>
@@ -1464,23 +1464,23 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=566</t>
+          <t>http://www.altonia.pr.gov.br/projeto-mais-educacao/projeto-mais-educacao-1/</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D38" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E38" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F38" t="inlineStr">
         <is>
-          <t>2026-07-29 10:47:59</t>
+          <t>2026-07-29 12:10:19</t>
         </is>
       </c>
     </row>
@@ -1492,23 +1492,23 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=561</t>
+          <t>http://www.altonia.pr.gov.br/projeto-mais-educacao/projeto-mais-educacao-5/</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D39" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E39" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F39" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:04</t>
+          <t>2026-07-29 12:10:20</t>
         </is>
       </c>
     </row>
@@ -1520,23 +1520,23 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=562</t>
+          <t>http://www.altonia.pr.gov.br/projeto-mais-educacao/projeto-mais-educacao-4/</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D40" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E40" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F40" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:08</t>
+          <t>2026-07-29 12:10:21</t>
         </is>
       </c>
     </row>
@@ -1548,23 +1548,23 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=555</t>
+          <t>http://www.altonia.pr.gov.br/palestra-empreendedorismo-feminino/empreendedorismo-feminino-1/</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D41" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E41" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F41" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:12</t>
+          <t>2026-07-29 12:10:21</t>
         </is>
       </c>
     </row>
@@ -1576,23 +1576,23 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=546</t>
+          <t>http://www.altonia.pr.gov.br/palestra-empreendedorismo-feminino/empreendedorismo-feminino-2/</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D42" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E42" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F42" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:18</t>
+          <t>2026-07-29 12:10:22</t>
         </is>
       </c>
     </row>
@@ -1604,23 +1604,23 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=544</t>
+          <t>http://www.altonia.pr.gov.br/palestra-empreendedorismo-feminino/empreendedorismo-feminino-3/</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D43" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E43" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F43" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:22</t>
+          <t>2026-07-29 12:10:23</t>
         </is>
       </c>
     </row>
@@ -1632,23 +1632,23 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=545</t>
+          <t>http://www.altonia.pr.gov.br/palestra-empreendedorismo-feminino/empreendedorismo-feminino-4/</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D44" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E44" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F44" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:26</t>
+          <t>2026-07-29 12:10:24</t>
         </is>
       </c>
     </row>
@@ -1660,23 +1660,23 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=531</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-planejar-3/oficina-sei-planejar-17-05-2015-1-2/</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D45" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E45" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F45" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:32</t>
+          <t>2026-07-29 12:10:25</t>
         </is>
       </c>
     </row>
@@ -1688,23 +1688,23 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=533</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-planejar-3/oficina-sei-planejar-17-05-2015-2-2/</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D46" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E46" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F46" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:35</t>
+          <t>2026-07-29 12:10:26</t>
         </is>
       </c>
     </row>
@@ -1716,23 +1716,23 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacaoView/?id=529</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-planejar-3/oficina-sei-planejar-17-05-2015-3-2/</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D47" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E47" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F47" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:39</t>
+          <t>2026-07-29 12:10:27</t>
         </is>
       </c>
     </row>
@@ -1744,23 +1744,23 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;pag=2</t>
+          <t>http://www.altonia.pr.gov.br/oficina-sei-planejar-3/oficina-sei-planejar-17-05-2015-4-2/</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D48" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E48" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F48" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:44</t>
+          <t>2026-07-29 12:10:28</t>
         </is>
       </c>
     </row>
@@ -1772,23 +1772,23 @@
       </c>
       <c r="B49" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;pag=3</t>
+          <t>http://www.altonia.pr.gov.br/inaugurada-a-nova-sala-do-empreendedor-em-altonia/nova-sala-1/</t>
         </is>
       </c>
       <c r="C49" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D49" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E49" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F49" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:48</t>
+          <t>2026-07-29 12:10:29</t>
         </is>
       </c>
     </row>
@@ -1800,23 +1800,23 @@
       </c>
       <c r="B50" t="inlineStr">
         <is>
-          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;pag=4</t>
+          <t>http://www.altonia.pr.gov.br/inaugurada-a-nova-sala-do-empreendedor-em-altonia/nova-sala-2/</t>
         </is>
       </c>
       <c r="C50" t="inlineStr">
         <is>
-          <t>HTTP_429</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D50" t="n">
-        <v>429</v>
+        <v>404</v>
       </c>
       <c r="E50" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F50" t="inlineStr">
         <is>
-          <t>2026-07-29 10:48:52</t>
+          <t>2026-07-29 12:10:30</t>
         </is>
       </c>
     </row>
@@ -1828,7 +1828,7 @@
       </c>
       <c r="B51" t="inlineStr">
         <is>
-          <t>https://www.altonia.pr.gov.br/pagina/_.html</t>
+          <t>http://www.altonia.pr.gov.br/inaugurada-a-nova-sala-do-empreendedor-em-altonia/nova-sala-3/</t>
         </is>
       </c>
       <c r="C51" t="inlineStr">
@@ -1840,11 +1840,11 @@
         <v>404</v>
       </c>
       <c r="E51" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="F51" t="inlineStr">
         <is>
-          <t>2026-07-29 10:50:24</t>
+          <t>2026-07-29 12:10:31</t>
         </is>
       </c>
     </row>
@@ -1856,23 +1856,23 @@
       </c>
       <c r="B52" t="inlineStr">
         <is>
-          <t>https://www.altonia.pr.gov.br/uploads/noticia/</t>
+          <t>http://www.altonia.pr.gov.br/inaugurada-a-nova-sala-do-empreendedor-em-altonia/nova-sala-4/</t>
         </is>
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>HTTP_403</t>
+          <t>HTTP_404</t>
         </is>
       </c>
       <c r="D52" t="n">
-        <v>403</v>
+        <v>404</v>
       </c>
       <c r="E52" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>2026-07-29 10:53:17</t>
+          <t>2026-07-29 12:10:32</t>
         </is>
       </c>
     </row>
@@ -1884,7 +1884,7 @@
       </c>
       <c r="B53" t="inlineStr">
         <is>
-          <t>https://www.altonia.pr.gov.br/noticiasView/16028_.html</t>
+          <t>http://www.altonia.pr.gov.br/inaugurada-a-nova-sala-do-empreendedor-em-altonia/nova-sala-5/</t>
         </is>
       </c>
       <c r="C53" t="inlineStr">
@@ -1896,11 +1896,11 @@
         <v>404</v>
       </c>
       <c r="E53" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F53" t="inlineStr">
         <is>
-          <t>2026-07-29 10:55:40</t>
+          <t>2026-07-29 12:10:33</t>
         </is>
       </c>
     </row>
@@ -1912,7 +1912,7 @@
       </c>
       <c r="B54" t="inlineStr">
         <is>
-          <t>https://www.altonia.pr.gov.br/noticiasView/15987_.html</t>
+          <t>http://www.altonia.pr.gov.br/wp-content/themes/NewsMash/galeria-pma.php</t>
         </is>
       </c>
       <c r="C54" t="inlineStr">
@@ -1924,11 +1924,11 @@
         <v>404</v>
       </c>
       <c r="E54" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="F54" t="inlineStr">
         <is>
-          <t>2026-07-29 10:55:45</t>
+          <t>2026-07-29 12:10:34</t>
         </is>
       </c>
     </row>
@@ -1940,7 +1940,7 @@
       </c>
       <c r="B55" t="inlineStr">
         <is>
-          <t>https://www.altonia.pr.gov.br/noticiasView/14829_.html</t>
+          <t>http://www.altonia.pr.gov.br/pagina/_.html</t>
         </is>
       </c>
       <c r="C55" t="inlineStr">
@@ -1952,11 +1952,1215 @@
         <v>404</v>
       </c>
       <c r="E55" t="n">
+        <v>7</v>
+      </c>
+      <c r="F55" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:43:21</t>
+        </is>
+      </c>
+    </row>
+    <row r="56">
+      <c r="A56" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B56" t="inlineStr">
+        <is>
+          <t>http://www.altonia.pr.gov.br/noticiasView/16028_.html</t>
+        </is>
+      </c>
+      <c r="C56" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D56" t="n">
+        <v>404</v>
+      </c>
+      <c r="E56" t="n">
+        <v>8</v>
+      </c>
+      <c r="F56" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:48:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="57">
+      <c r="A57" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B57" t="inlineStr">
+        <is>
+          <t>http://www.altonia.pr.gov.br/noticiasView/15987_.html</t>
+        </is>
+      </c>
+      <c r="C57" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D57" t="n">
+        <v>404</v>
+      </c>
+      <c r="E57" t="n">
+        <v>8</v>
+      </c>
+      <c r="F57" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:48:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="58">
+      <c r="A58" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B58" t="inlineStr">
+        <is>
+          <t>http://www.altonia.pr.gov.br/noticiasView/14829_.html</t>
+        </is>
+      </c>
+      <c r="C58" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D58" t="n">
+        <v>404</v>
+      </c>
+      <c r="E58" t="n">
+        <v>8</v>
+      </c>
+      <c r="F58" t="inlineStr">
+        <is>
+          <t>2026-07-29 12:51:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="59">
+      <c r="A59" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B59" t="inlineStr">
+        <is>
+          <t>https://webapp1-altonia.cidade360.cloud/PRONIMTB/index.html/</t>
+        </is>
+      </c>
+      <c r="C59" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D59" t="n">
+        <v>404</v>
+      </c>
+      <c r="E59" t="n">
+        <v>0</v>
+      </c>
+      <c r="F59" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:03</t>
+        </is>
+      </c>
+    </row>
+    <row r="60">
+      <c r="A60" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B60" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=584</t>
+        </is>
+      </c>
+      <c r="C60" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D60" t="n">
+        <v>429</v>
+      </c>
+      <c r="E60" t="n">
+        <v>2</v>
+      </c>
+      <c r="F60" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:04</t>
+        </is>
+      </c>
+    </row>
+    <row r="61">
+      <c r="A61" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B61" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=572</t>
+        </is>
+      </c>
+      <c r="C61" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D61" t="n">
+        <v>429</v>
+      </c>
+      <c r="E61" t="n">
+        <v>2</v>
+      </c>
+      <c r="F61" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="62">
+      <c r="A62" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B62" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;pag=4</t>
+        </is>
+      </c>
+      <c r="C62" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D62" t="n">
+        <v>429</v>
+      </c>
+      <c r="E62" t="n">
+        <v>2</v>
+      </c>
+      <c r="F62" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="63">
+      <c r="A63" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B63" t="inlineStr">
+        <is>
+          <t>https://www.altonia.pr.gov.br/uploads/noticia/</t>
+        </is>
+      </c>
+      <c r="C63" t="inlineStr">
+        <is>
+          <t>HTTP_403</t>
+        </is>
+      </c>
+      <c r="D63" t="n">
+        <v>403</v>
+      </c>
+      <c r="E63" t="n">
         <v>3</v>
       </c>
-      <c r="F55" t="inlineStr">
-        <is>
-          <t>2026-07-29 10:58:23</t>
+      <c r="F63" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:17</t>
+        </is>
+      </c>
+    </row>
+    <row r="64">
+      <c r="A64" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B64" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=429</t>
+        </is>
+      </c>
+      <c r="C64" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D64" t="n">
+        <v>429</v>
+      </c>
+      <c r="E64" t="n">
+        <v>3</v>
+      </c>
+      <c r="F64" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:24</t>
+        </is>
+      </c>
+    </row>
+    <row r="65">
+      <c r="A65" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B65" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=412</t>
+        </is>
+      </c>
+      <c r="C65" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D65" t="n">
+        <v>429</v>
+      </c>
+      <c r="E65" t="n">
+        <v>3</v>
+      </c>
+      <c r="F65" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:28</t>
+        </is>
+      </c>
+    </row>
+    <row r="66">
+      <c r="A66" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B66" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=410</t>
+        </is>
+      </c>
+      <c r="C66" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D66" t="n">
+        <v>429</v>
+      </c>
+      <c r="E66" t="n">
+        <v>3</v>
+      </c>
+      <c r="F66" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:32</t>
+        </is>
+      </c>
+    </row>
+    <row r="67">
+      <c r="A67" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B67" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=201</t>
+        </is>
+      </c>
+      <c r="C67" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D67" t="n">
+        <v>429</v>
+      </c>
+      <c r="E67" t="n">
+        <v>3</v>
+      </c>
+      <c r="F67" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="68">
+      <c r="A68" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B68" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=200</t>
+        </is>
+      </c>
+      <c r="C68" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D68" t="n">
+        <v>429</v>
+      </c>
+      <c r="E68" t="n">
+        <v>3</v>
+      </c>
+      <c r="F68" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="69">
+      <c r="A69" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B69" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=185</t>
+        </is>
+      </c>
+      <c r="C69" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D69" t="n">
+        <v>429</v>
+      </c>
+      <c r="E69" t="n">
+        <v>3</v>
+      </c>
+      <c r="F69" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:45</t>
+        </is>
+      </c>
+    </row>
+    <row r="70">
+      <c r="A70" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B70" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=79</t>
+        </is>
+      </c>
+      <c r="C70" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D70" t="n">
+        <v>429</v>
+      </c>
+      <c r="E70" t="n">
+        <v>3</v>
+      </c>
+      <c r="F70" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:52</t>
+        </is>
+      </c>
+    </row>
+    <row r="71">
+      <c r="A71" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B71" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=459</t>
+        </is>
+      </c>
+      <c r="C71" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D71" t="n">
+        <v>429</v>
+      </c>
+      <c r="E71" t="n">
+        <v>3</v>
+      </c>
+      <c r="F71" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:20:56</t>
+        </is>
+      </c>
+    </row>
+    <row r="72">
+      <c r="A72" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B72" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=458</t>
+        </is>
+      </c>
+      <c r="C72" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D72" t="n">
+        <v>429</v>
+      </c>
+      <c r="E72" t="n">
+        <v>3</v>
+      </c>
+      <c r="F72" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="73">
+      <c r="A73" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B73" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=365</t>
+        </is>
+      </c>
+      <c r="C73" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D73" t="n">
+        <v>429</v>
+      </c>
+      <c r="E73" t="n">
+        <v>3</v>
+      </c>
+      <c r="F73" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:05</t>
+        </is>
+      </c>
+    </row>
+    <row r="74">
+      <c r="A74" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B74" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=10&amp;ano=2025&amp;pag=3</t>
+        </is>
+      </c>
+      <c r="C74" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D74" t="n">
+        <v>429</v>
+      </c>
+      <c r="E74" t="n">
+        <v>3</v>
+      </c>
+      <c r="F74" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:09</t>
+        </is>
+      </c>
+    </row>
+    <row r="75">
+      <c r="A75" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B75" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=218</t>
+        </is>
+      </c>
+      <c r="C75" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D75" t="n">
+        <v>429</v>
+      </c>
+      <c r="E75" t="n">
+        <v>3</v>
+      </c>
+      <c r="F75" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:13</t>
+        </is>
+      </c>
+    </row>
+    <row r="76">
+      <c r="A76" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B76" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=105</t>
+        </is>
+      </c>
+      <c r="C76" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D76" t="n">
+        <v>429</v>
+      </c>
+      <c r="E76" t="n">
+        <v>3</v>
+      </c>
+      <c r="F76" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="77">
+      <c r="A77" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B77" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/uploads/noticia/</t>
+        </is>
+      </c>
+      <c r="C77" t="inlineStr">
+        <is>
+          <t>HTTP_403</t>
+        </is>
+      </c>
+      <c r="D77" t="n">
+        <v>403</v>
+      </c>
+      <c r="E77" t="n">
+        <v>4</v>
+      </c>
+      <c r="F77" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:23</t>
+        </is>
+      </c>
+    </row>
+    <row r="78">
+      <c r="A78" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B78" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/concursos/index.php?idCategoriaConcurso={{categoria.id}}&amp;idCategoriaConcurso={{categoria.id}}</t>
+        </is>
+      </c>
+      <c r="C78" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D78" t="n">
+        <v>429</v>
+      </c>
+      <c r="E78" t="n">
+        <v>4</v>
+      </c>
+      <c r="F78" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:27</t>
+        </is>
+      </c>
+    </row>
+    <row r="79">
+      <c r="A79" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B79" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=377</t>
+        </is>
+      </c>
+      <c r="C79" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D79" t="n">
+        <v>429</v>
+      </c>
+      <c r="E79" t="n">
+        <v>4</v>
+      </c>
+      <c r="F79" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:33</t>
+        </is>
+      </c>
+    </row>
+    <row r="80">
+      <c r="A80" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B80" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=334</t>
+        </is>
+      </c>
+      <c r="C80" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D80" t="n">
+        <v>429</v>
+      </c>
+      <c r="E80" t="n">
+        <v>4</v>
+      </c>
+      <c r="F80" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="81">
+      <c r="A81" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B81" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=319</t>
+        </is>
+      </c>
+      <c r="C81" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D81" t="n">
+        <v>429</v>
+      </c>
+      <c r="E81" t="n">
+        <v>4</v>
+      </c>
+      <c r="F81" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:41</t>
+        </is>
+      </c>
+    </row>
+    <row r="82">
+      <c r="A82" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B82" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=271</t>
+        </is>
+      </c>
+      <c r="C82" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D82" t="n">
+        <v>429</v>
+      </c>
+      <c r="E82" t="n">
+        <v>4</v>
+      </c>
+      <c r="F82" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="83">
+      <c r="A83" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B83" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=290</t>
+        </is>
+      </c>
+      <c r="C83" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D83" t="n">
+        <v>429</v>
+      </c>
+      <c r="E83" t="n">
+        <v>4</v>
+      </c>
+      <c r="F83" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="84">
+      <c r="A84" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B84" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacaoView/?id=278</t>
+        </is>
+      </c>
+      <c r="C84" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D84" t="n">
+        <v>429</v>
+      </c>
+      <c r="E84" t="n">
+        <v>4</v>
+      </c>
+      <c r="F84" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:21:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="85">
+      <c r="A85" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B85" t="inlineStr">
+        <is>
+          <t>http://www.altonia.pr.gov.br/?attachment_id=1993</t>
+        </is>
+      </c>
+      <c r="C85" t="inlineStr">
+        <is>
+          <t>HTTP_403</t>
+        </is>
+      </c>
+      <c r="D85" t="n">
+        <v>403</v>
+      </c>
+      <c r="E85" t="n">
+        <v>5</v>
+      </c>
+      <c r="F85" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="86">
+      <c r="A86" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B86" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=1&amp;ano=2025&amp;pag=3</t>
+        </is>
+      </c>
+      <c r="C86" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D86" t="n">
+        <v>429</v>
+      </c>
+      <c r="E86" t="n">
+        <v>5</v>
+      </c>
+      <c r="F86" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:07</t>
+        </is>
+      </c>
+    </row>
+    <row r="87">
+      <c r="A87" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B87" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=1&amp;ano=2025&amp;pag=9</t>
+        </is>
+      </c>
+      <c r="C87" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D87" t="n">
+        <v>429</v>
+      </c>
+      <c r="E87" t="n">
+        <v>5</v>
+      </c>
+      <c r="F87" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:11</t>
+        </is>
+      </c>
+    </row>
+    <row r="88">
+      <c r="A88" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B88" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=1&amp;ano=2025&amp;pag=10</t>
+        </is>
+      </c>
+      <c r="C88" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D88" t="n">
+        <v>429</v>
+      </c>
+      <c r="E88" t="n">
+        <v>5</v>
+      </c>
+      <c r="F88" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:14</t>
+        </is>
+      </c>
+    </row>
+    <row r="89">
+      <c r="A89" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B89" t="inlineStr">
+        <is>
+          <t>http://www.altonia.pr.gov.br/uploads/noticia/</t>
+        </is>
+      </c>
+      <c r="C89" t="inlineStr">
+        <is>
+          <t>HTTP_403</t>
+        </is>
+      </c>
+      <c r="D89" t="n">
+        <v>403</v>
+      </c>
+      <c r="E89" t="n">
+        <v>8</v>
+      </c>
+      <c r="F89" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:19</t>
+        </is>
+      </c>
+    </row>
+    <row r="90">
+      <c r="A90" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B90" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=2&amp;ano=2022&amp;idCategoriaLegislacao=1</t>
+        </is>
+      </c>
+      <c r="C90" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D90" t="n">
+        <v>429</v>
+      </c>
+      <c r="E90" t="n">
+        <v>5</v>
+      </c>
+      <c r="F90" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:26</t>
+        </is>
+      </c>
+    </row>
+    <row r="91">
+      <c r="A91" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B91" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=2&amp;ano=2022&amp;idCategoriaLegislacao=3</t>
+        </is>
+      </c>
+      <c r="C91" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D91" t="n">
+        <v>429</v>
+      </c>
+      <c r="E91" t="n">
+        <v>5</v>
+      </c>
+      <c r="F91" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:29</t>
+        </is>
+      </c>
+    </row>
+    <row r="92">
+      <c r="A92" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B92" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/servico/requerimento-de-alvara-sanitario/executar.html</t>
+        </is>
+      </c>
+      <c r="C92" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D92" t="n">
+        <v>404</v>
+      </c>
+      <c r="E92" t="n">
+        <v>3</v>
+      </c>
+      <c r="F92" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:37</t>
+        </is>
+      </c>
+    </row>
+    <row r="93">
+      <c r="A93" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B93" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=1&amp;pag=6</t>
+        </is>
+      </c>
+      <c r="C93" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D93" t="n">
+        <v>429</v>
+      </c>
+      <c r="E93" t="n">
+        <v>4</v>
+      </c>
+      <c r="F93" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:46</t>
+        </is>
+      </c>
+    </row>
+    <row r="94">
+      <c r="A94" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B94" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=1&amp;pag=7</t>
+        </is>
+      </c>
+      <c r="C94" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D94" t="n">
+        <v>429</v>
+      </c>
+      <c r="E94" t="n">
+        <v>4</v>
+      </c>
+      <c r="F94" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:50</t>
+        </is>
+      </c>
+    </row>
+    <row r="95">
+      <c r="A95" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B95" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idStatusLegislacao=1&amp;pag=8</t>
+        </is>
+      </c>
+      <c r="C95" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D95" t="n">
+        <v>429</v>
+      </c>
+      <c r="E95" t="n">
+        <v>4</v>
+      </c>
+      <c r="F95" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:22:54</t>
+        </is>
+      </c>
+    </row>
+    <row r="96">
+      <c r="A96" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B96" t="inlineStr">
+        <is>
+          <t>https://altonia.pr.gov.br/legislacao/?idCategoriaLegislacao=1&amp;ano=2026&amp;pag=1</t>
+        </is>
+      </c>
+      <c r="C96" t="inlineStr">
+        <is>
+          <t>HTTP_429</t>
+        </is>
+      </c>
+      <c r="D96" t="n">
+        <v>429</v>
+      </c>
+      <c r="E96" t="n">
+        <v>4</v>
+      </c>
+      <c r="F96" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:23:00</t>
+        </is>
+      </c>
+    </row>
+    <row r="97">
+      <c r="A97" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B97" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/servico/executar.html</t>
+        </is>
+      </c>
+      <c r="C97" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D97" t="n">
+        <v>404</v>
+      </c>
+      <c r="E97" t="n">
+        <v>3</v>
+      </c>
+      <c r="F97" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:23:30</t>
+        </is>
+      </c>
+    </row>
+    <row r="98">
+      <c r="A98" t="inlineStr">
+        <is>
+          <t>altonia</t>
+        </is>
+      </c>
+      <c r="B98" t="inlineStr">
+        <is>
+          <t>https://altonia.cidade360.cloud/portal-servicos/servico/avaliar.html</t>
+        </is>
+      </c>
+      <c r="C98" t="inlineStr">
+        <is>
+          <t>HTTP_404</t>
+        </is>
+      </c>
+      <c r="D98" t="n">
+        <v>404</v>
+      </c>
+      <c r="E98" t="n">
+        <v>3</v>
+      </c>
+      <c r="F98" t="inlineStr">
+        <is>
+          <t>2026-07-30 01:23:30</t>
         </is>
       </c>
     </row>
